--- a/server/public/template.xlsx
+++ b/server/public/template.xlsx
@@ -1,58 +1,548 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="29400" windowHeight="14620"/>
+  </bookViews>
   <sheets>
     <sheet name="医院数据" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>行政区划代码</t>
+  </si>
+  <si>
+    <t>医院名称</t>
+  </si>
+  <si>
+    <t>门诊名称</t>
+  </si>
+  <si>
+    <t>出诊人员</t>
+  </si>
+  <si>
+    <t>周一上午</t>
+  </si>
+  <si>
+    <t>周一下午</t>
+  </si>
+  <si>
+    <t>周二上午</t>
+  </si>
+  <si>
+    <t>周二下午</t>
+  </si>
+  <si>
+    <t>周三上午</t>
+  </si>
+  <si>
+    <t>周三下午</t>
+  </si>
+  <si>
+    <t>周四上午</t>
+  </si>
+  <si>
+    <t>周四下午</t>
+  </si>
+  <si>
+    <t>周五上午</t>
+  </si>
+  <si>
+    <t>周五下午</t>
+  </si>
+  <si>
+    <t>周六上午</t>
+  </si>
+  <si>
+    <t>周六下午</t>
+  </si>
+  <si>
+    <t>周日上午</t>
+  </si>
+  <si>
+    <t>周日下午</t>
+  </si>
+  <si>
+    <t>西安市</t>
+  </si>
+  <si>
+    <t>空军军医大学第一附属医院（西京医院）</t>
+  </si>
+  <si>
+    <t>造口伤口护理门诊</t>
+  </si>
+  <si>
+    <t>张三、李四、王五</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>尿控（造口）护理门诊</t>
+  </si>
+  <si>
+    <t>李四、王五</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5930"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF7F9FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -60,18 +550,347 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DEE7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9DEE7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9DEE7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9DEE7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF5930"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -391,295 +1210,383 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:S29"/>
+  <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="17.6"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" customWidth="1"/>
-    <col min="6" max="6" width="16.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" customWidth="1"/>
-    <col min="10" max="10" width="8.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="8.83203125" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" customWidth="1"/>
-    <col min="14" max="14" width="8.83203125" customWidth="1"/>
-    <col min="15" max="15" width="8.83203125" customWidth="1"/>
-    <col min="16" max="16" width="8.83203125" customWidth="1"/>
-    <col min="17" max="17" width="8.83203125" customWidth="1"/>
-    <col min="18" max="18" width="8.83203125" customWidth="1"/>
-    <col min="19" max="19" width="8.83203125" customWidth="1"/>
-    <col min="20" max="20" width="8.83203125" customWidth="1"/>
-    <col min="21" max="21" width="8.83203125" customWidth="1"/>
-    <col min="22" max="22" width="8.83203125" customWidth="1"/>
-    <col min="23" max="23" width="8.83203125" customWidth="1"/>
-    <col min="24" max="24" width="8.83203125" customWidth="1"/>
-    <col min="25" max="25" width="8.83203125" customWidth="1"/>
-    <col min="26" max="26" width="8.83203125" customWidth="1"/>
-    <col min="27" max="27" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="12.8303571428571" customWidth="1"/>
+    <col min="2" max="2" width="14.8303571428571" customWidth="1"/>
+    <col min="3" max="3" width="30.8303571428571" customWidth="1"/>
+    <col min="4" max="4" width="24.8303571428571" customWidth="1"/>
+    <col min="5" max="5" width="16.8303571428571" customWidth="1"/>
+    <col min="6" max="6" width="8.83035714285714" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83035714285714" style="2" customWidth="1"/>
+    <col min="8" max="9" width="8.83035714285714" style="3" customWidth="1"/>
+    <col min="10" max="11" width="8.83035714285714" style="4" customWidth="1"/>
+    <col min="12" max="13" width="8.83035714285714" style="5" customWidth="1"/>
+    <col min="14" max="15" width="8.83035714285714" style="6" customWidth="1"/>
+    <col min="16" max="17" width="8.83035714285714" style="7" customWidth="1"/>
+    <col min="18" max="19" width="8.83035714285714" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>序号</v>
-      </c>
-      <c r="B1" t="str">
-        <v>城市</v>
-      </c>
-      <c r="C1" t="str">
-        <v>行政区划代码</v>
-      </c>
-      <c r="D1" t="str">
-        <v>医院名称</v>
-      </c>
-      <c r="E1" t="str">
-        <v>门诊名称</v>
-      </c>
-      <c r="F1" t="str">
-        <v>出诊人员</v>
-      </c>
-      <c r="G1" t="str">
-        <v>周一上午</v>
-      </c>
-      <c r="H1" t="str">
-        <v>周一下午</v>
-      </c>
-      <c r="I1" t="str">
-        <v>周一晚上</v>
-      </c>
-      <c r="J1" t="str">
-        <v>周二上午</v>
-      </c>
-      <c r="K1" t="str">
-        <v>周二下午</v>
-      </c>
-      <c r="L1" t="str">
-        <v>周二晚上</v>
-      </c>
-      <c r="M1" t="str">
-        <v>周三上午</v>
-      </c>
-      <c r="N1" t="str">
-        <v>周三下午</v>
-      </c>
-      <c r="O1" t="str">
-        <v>周三晚上</v>
-      </c>
-      <c r="P1" t="str">
-        <v>周四上午</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>周四下午</v>
-      </c>
-      <c r="R1" t="str">
-        <v>周四晚上</v>
-      </c>
-      <c r="S1" t="str">
-        <v>周五上午</v>
-      </c>
-      <c r="T1" t="str">
-        <v>周五下午</v>
-      </c>
-      <c r="U1" t="str">
-        <v>周五晚上</v>
-      </c>
-      <c r="V1" t="str">
-        <v>周六上午</v>
-      </c>
-      <c r="W1" t="str">
-        <v>周六下午</v>
-      </c>
-      <c r="X1" t="str">
-        <v>周六晚上</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>周日上午</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>周日下午</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>周日晚上</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
+    <row r="1" spans="1:19">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="str">
-        <v>西安市</v>
-      </c>
-      <c r="C2" t="str">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" ht="31" spans="1:19">
+      <c r="A2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="10">
         <v>610100</v>
       </c>
-      <c r="D2" t="str">
-        <v>西安交通大学第一附属医院</v>
-      </c>
-      <c r="E2" t="str">
-        <v>造口伤口护理门诊</v>
-      </c>
-      <c r="F2" t="str">
-        <v>张三</v>
-      </c>
-      <c r="G2">
+      <c r="C2" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="1">
         <v>1</v>
       </c>
-      <c r="H2">
+      <c r="G2" s="2">
         <v>1</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2">
+      <c r="H2" s="3">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2">
+      <c r="K2" s="4">
         <v>1</v>
       </c>
-      <c r="N2">
+      <c r="L2" s="5">
         <v>1</v>
       </c>
-      <c r="O2" t="str">
-        <v/>
-      </c>
-      <c r="P2">
+      <c r="M2" s="5">
         <v>1</v>
       </c>
-      <c r="Q2">
+      <c r="N2" s="6">
         <v>1</v>
       </c>
-      <c r="R2" t="str">
-        <v/>
-      </c>
-      <c r="S2">
+      <c r="P2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" ht="31" spans="1:19">
+      <c r="A3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="10">
+        <v>610100</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="H3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" s="6">
         <v>1</v>
       </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2" t="str">
-        <v/>
-      </c>
-      <c r="V2" t="str">
-        <v/>
-      </c>
-      <c r="W2" t="str">
-        <v/>
-      </c>
-      <c r="X2" t="str">
-        <v/>
-      </c>
-      <c r="Y2" t="str">
-        <v/>
-      </c>
-      <c r="Z2" t="str">
-        <v/>
-      </c>
-      <c r="AA2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>西安市</v>
-      </c>
-      <c r="C3" t="str">
-        <v>610100</v>
-      </c>
-      <c r="D3" t="str">
-        <v>西安交通大学第一附属医院</v>
-      </c>
-      <c r="E3" t="str">
-        <v>静脉门诊</v>
-      </c>
-      <c r="F3" t="str">
-        <v>李四、王五</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-      <c r="U3">
-        <v>1</v>
-      </c>
-      <c r="V3" t="str">
-        <v/>
-      </c>
-      <c r="W3" t="str">
-        <v/>
-      </c>
-      <c r="X3" t="str">
-        <v/>
-      </c>
-      <c r="Y3" t="str">
-        <v/>
-      </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
-      <c r="AA3" t="str">
-        <v/>
-      </c>
+      <c r="P3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R3" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="S3" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="11"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="11"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="11"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="11"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="9"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="11"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="11"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="9"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="11"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="9"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="11"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="9"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="11"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="11"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="11"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="11"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="9"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="11"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AA3"/>
+    <ignoredError sqref="P2:S2 J2:M2 F2:G2 A1:S1 P3:S3 H3:N3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>